--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_15.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_15.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Treatment?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>InformationLevel</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.2232957756137529</v>
+        <v>-0.4123420068938169</v>
       </c>
       <c r="C2">
-        <v>-0.3799016043773061</v>
+        <v>0.3659725196817725</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5269745677648229</v>
+        <v>1.210867713153746</v>
       </c>
       <c r="C3">
-        <v>0.892936211765649</v>
+        <v>0.7323560712279077</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.174760861200671</v>
+        <v>0.3308440272277923</v>
       </c>
       <c r="C4">
-        <v>-1.26940120380786</v>
+        <v>1.024698584390742</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.3793166432292219</v>
+        <v>-0.05321488149236028</v>
       </c>
       <c r="C5">
-        <v>1.417142980191733</v>
+        <v>0.2837806445077392</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.9126529619627031</v>
+        <v>-0.5091170955793834</v>
       </c>
       <c r="C6">
-        <v>-0.4964460246508816</v>
+        <v>-1.303807064373614</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.2346768138742133</v>
+        <v>0.3053492276319672</v>
       </c>
       <c r="C7">
-        <v>-0.05440353778767925</v>
+        <v>0.4024784576550292</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.8765496147992695</v>
+        <v>-1.723352462880568</v>
       </c>
       <c r="C8">
-        <v>-0.2026099026461853</v>
+        <v>-0.8676870293514868</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.4920112393040629</v>
+        <v>-0.8392971990634882</v>
       </c>
       <c r="C9">
-        <v>0.05204492200024349</v>
+        <v>-1.148111553906176</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.5652628678109528</v>
+        <v>0.7942779061965424</v>
       </c>
       <c r="C10">
-        <v>0.6298071299520215</v>
+        <v>0.9733861032490488</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.2675341691681475</v>
+        <v>-0.8506606385337557</v>
       </c>
       <c r="C11">
-        <v>0.4199062810815065</v>
+        <v>-0.5130098412447398</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.866944060088117</v>
+        <v>0.198920106556511</v>
       </c>
       <c r="C12">
-        <v>-1.398672103469469</v>
+        <v>1.204562763749778</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.3637538578003386</v>
+        <v>-1.557212031322621</v>
       </c>
       <c r="C13">
-        <v>0.3092868614140937</v>
+        <v>-0.8616786872938078</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.57416908231188</v>
+        <v>-0.8234765308784229</v>
       </c>
       <c r="C14">
-        <v>0.5416919513020613</v>
+        <v>-0.4295687026329387</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.04806451185916912</v>
+        <v>-1.19197488000393</v>
       </c>
       <c r="C15">
-        <v>0.401540164204677</v>
+        <v>-1.088936887657209</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.8738849793234411</v>
+        <v>-1.585374306503025</v>
       </c>
       <c r="C16">
-        <v>-1.099175975072392</v>
+        <v>-0.5561417294081944</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.07658900097999438</v>
+        <v>0.0429693088296793</v>
       </c>
       <c r="C17">
-        <v>0.1319154125654485</v>
+        <v>-0.1720546901534435</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-1.405356436104402</v>
+        <v>0.8867655523196564</v>
       </c>
       <c r="C18">
-        <v>0.473788335953187</v>
+        <v>-1.594593860874175</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.4620849220414298</v>
+        <v>-1.272359574629454</v>
       </c>
       <c r="C19">
-        <v>-1.02269510007502</v>
+        <v>-0.6100288999407656</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.549514482391373</v>
+        <v>1.476605712564065</v>
       </c>
       <c r="C20">
-        <v>0.3914283348721686</v>
+        <v>1.031992737573186</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.6093722890477833</v>
+        <v>-1.892562446675193</v>
       </c>
       <c r="C21">
-        <v>-0.21496898224587</v>
+        <v>-1.037419530151591</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.6344154865577907</v>
+        <v>-0.8581011448062664</v>
       </c>
       <c r="C22">
-        <v>-0.496382189616082</v>
+        <v>1.505535081623981</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.08339374280379164</v>
+        <v>0.8642997560445776</v>
       </c>
       <c r="C23">
-        <v>-0.3502182032057592</v>
+        <v>-0.2345119258497619</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.73553904421143</v>
+        <v>0.1968303559110145</v>
       </c>
       <c r="C24">
-        <v>-1.58190682568738</v>
+        <v>-0.1042727181583958</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.8634772292130654</v>
+        <v>0.0912659661301149</v>
       </c>
       <c r="C25">
-        <v>0.3592870027846767</v>
+        <v>-0.1752327999607708</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.6436926127885561</v>
+        <v>0.3964383001352649</v>
       </c>
       <c r="C26">
-        <v>-0.3529986441894666</v>
+        <v>0.9274460652421794</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.336751858611123</v>
+        <v>0.7878602060489401</v>
       </c>
       <c r="C27">
-        <v>0.6186708870636145</v>
+        <v>0.5483475091670017</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.290726362081991</v>
+        <v>-0.3589941365952894</v>
       </c>
       <c r="C28">
-        <v>1.501716390193862</v>
+        <v>0.5533117146818353</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.5253428921272653</v>
+        <v>-1.46876677545867</v>
       </c>
       <c r="C29">
-        <v>0.445253252072428</v>
+        <v>-0.6470298741163565</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.030650265476197</v>
+        <v>0.2100862286707986</v>
       </c>
       <c r="C30">
-        <v>1.205944761848681</v>
+        <v>0.4397069312103901</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.832185520735676</v>
+        <v>1.125995150609968</v>
       </c>
       <c r="C31">
-        <v>-1.480339566448772</v>
+        <v>-0.07180514596200976</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.7951822304909369</v>
+        <v>0.0739875939689538</v>
       </c>
       <c r="C32">
-        <v>0.9061690396513954</v>
+        <v>0.7026302528637796</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.33764048242721</v>
+        <v>1.294012867668879</v>
       </c>
       <c r="C33">
-        <v>0.2114570859531695</v>
+        <v>0.5929541532448628</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.3652150603917934</v>
+        <v>-1.310142224268697</v>
       </c>
       <c r="C34">
-        <v>-0.01757095706122488</v>
+        <v>-0.4440271816628058</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.8627067416405844</v>
+        <v>-0.5722758646146984</v>
       </c>
       <c r="C35">
-        <v>0.3954060236430452</v>
+        <v>-0.2273011580194361</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.8280511565755488</v>
+        <v>-1.557121175023969</v>
       </c>
       <c r="C36">
-        <v>-0.6247515245018938</v>
+        <v>0.03262881446086474</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.3075812980792543</v>
+        <v>-1.709972028229532</v>
       </c>
       <c r="C37">
-        <v>1.370898477197395</v>
+        <v>-1.267970274098823</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.1579263410419797</v>
+        <v>-1.211267865531259</v>
       </c>
       <c r="C38">
-        <v>0.7426383708991181</v>
+        <v>-1.141301570687612</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-1.54135208607509</v>
+        <v>-0.2300634811021633</v>
       </c>
       <c r="C39">
-        <v>1.634341807930779</v>
+        <v>0.03550013862426528</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.8956107699647005</v>
+        <v>0.1563304900291876</v>
       </c>
       <c r="C40">
-        <v>1.614271678830339</v>
+        <v>-0.1434012880443539</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.6737904725304021</v>
+        <v>-0.4587644108340222</v>
       </c>
       <c r="C41">
-        <v>1.505365631543948</v>
+        <v>0.6724065227433754</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.02765200321751303</v>
+        <v>-0.6798108736425401</v>
       </c>
       <c r="C42">
-        <v>0.0366824254264588</v>
+        <v>0.3364616996324032</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.6292263350307615</v>
+        <v>0.4488607824639874</v>
       </c>
       <c r="C43">
-        <v>-0.7272768428436555</v>
+        <v>0.1420100623927439</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.9285573914388625</v>
+        <v>-0.7959430411192272</v>
       </c>
       <c r="C44">
-        <v>1.429070893673437</v>
+        <v>0.06172213321934256</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.3210202447508047</v>
+        <v>-1.816841330931485</v>
       </c>
       <c r="C45">
-        <v>0.6592077781907013</v>
+        <v>-0.4019656295812238</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.979360412842066</v>
+        <v>0.6493056605518909</v>
       </c>
       <c r="C46">
-        <v>-0.2939043657911069</v>
+        <v>-0.7439045864235287</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.400029686059392</v>
+        <v>-0.2097328439420846</v>
       </c>
       <c r="C47">
-        <v>0.8781735042924279</v>
+        <v>0.03538149317340532</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.1158661868610565</v>
+        <v>1.060698640092521</v>
       </c>
       <c r="C48">
-        <v>-2.026754337402235</v>
+        <v>0.8560849544051545</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.03567961139775239</v>
+        <v>0.02975108031011817</v>
       </c>
       <c r="C49">
-        <v>-1.643348466375186</v>
+        <v>0.08844412691738474</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.3539143548995909</v>
+        <v>0.5141469293645501</v>
       </c>
       <c r="C50">
-        <v>0.6584626385504212</v>
+        <v>-0.9449715868433481</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-2.019722522963032</v>
+        <v>0.09952773640564588</v>
       </c>
       <c r="C51">
-        <v>0.8808873573461542</v>
+        <v>0.180047586116821</v>
       </c>
     </row>
   </sheetData>
